--- a/data/pack/ca/novillo_ab.xlsx
+++ b/data/pack/ca/novillo_ab.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Datos" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fuente y licencia" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Datos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Fuente y licencia" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K88"/>
+  <dimension ref="A1:K89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5274,6 +5274,61 @@
         </is>
       </c>
       <c r="K88" t="inlineStr">
+        <is>
+          <t>Contains information licensed under the Open Government Licence – Alberta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>novillo_ab</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Novillos, ventas directas (Alberta)</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>298.3</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>cwt</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>CAD</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>Alberta Agriculture and Irrigation — Weekly Market Review</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>OGL-Alberta</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
         <is>
           <t>Contains information licensed under the Open Government Licence – Alberta.</t>
         </is>
@@ -5377,7 +5432,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-16</t>
         </is>
       </c>
     </row>
@@ -5388,7 +5443,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="9">
@@ -5483,7 +5538,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>

--- a/data/pack/ca/novillo_ab.xlsx
+++ b/data/pack/ca/novillo_ab.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K89"/>
+  <dimension ref="A1:K90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5329,6 +5329,61 @@
         </is>
       </c>
       <c r="K89" t="inlineStr">
+        <is>
+          <t>Contains information licensed under the Open Government Licence – Alberta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>novillo_ab</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Novillos, ventas directas (Alberta)</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>297.97</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>cwt</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>CAD</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>Alberta Agriculture and Irrigation — Weekly Market Review</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>OGL-Alberta</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
         <is>
           <t>Contains information licensed under the Open Government Licence – Alberta.</t>
         </is>
@@ -5432,7 +5487,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
@@ -5443,7 +5498,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="9">
@@ -5538,7 +5593,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>

--- a/data/pack/ca/novillo_ab.xlsx
+++ b/data/pack/ca/novillo_ab.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K90"/>
+  <dimension ref="A1:K91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5384,6 +5384,61 @@
         </is>
       </c>
       <c r="K90" t="inlineStr">
+        <is>
+          <t>Contains information licensed under the Open Government Licence – Alberta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>novillo_ab</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Novillos, ventas directas (Alberta)</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>296.61</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>cwt</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>CAD</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>Alberta Agriculture and Irrigation — Weekly Market Review</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>OGL-Alberta</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
         <is>
           <t>Contains information licensed under the Open Government Licence – Alberta.</t>
         </is>
@@ -5487,7 +5542,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -5498,7 +5553,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="9">
@@ -5593,7 +5648,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
